--- a/diseases/d004/2015-2019.xlsx
+++ b/diseases/d004/2015-2019.xlsx
@@ -8908,9 +8908,6 @@
       <c r="P57" t="n">
         <v>0</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0</v>
       </c>
@@ -9320,9 +9317,6 @@
       <c r="P59" t="n">
         <v>0</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0</v>
       </c>
@@ -9732,9 +9726,6 @@
       <c r="P61" t="n">
         <v>0</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0</v>
       </c>
@@ -10144,9 +10135,6 @@
       <c r="P63" t="n">
         <v>0</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0</v>
       </c>
@@ -10556,9 +10544,6 @@
       <c r="P65" t="n">
         <v>0</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0</v>
       </c>
@@ -11116,9 +11101,6 @@
       <c r="P68" t="n">
         <v>0</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0</v>
       </c>
@@ -11528,9 +11510,6 @@
       <c r="P70" t="n">
         <v>0</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0</v>
       </c>
@@ -11940,9 +11919,6 @@
       <c r="P72" t="n">
         <v>0</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0</v>
       </c>
@@ -12352,9 +12328,6 @@
       <c r="P74" t="n">
         <v>0</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0</v>
       </c>
@@ -12912,9 +12885,6 @@
       <c r="P77" t="n">
         <v>0</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0</v>
       </c>
@@ -13324,9 +13294,6 @@
       <c r="P79" t="n">
         <v>0</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0</v>
       </c>
@@ -13736,9 +13703,6 @@
       <c r="P81" t="n">
         <v>0</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>0</v>
       </c>
@@ -14148,9 +14112,6 @@
       <c r="P83" t="n">
         <v>0</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0</v>
       </c>
@@ -14560,9 +14521,6 @@
       <c r="P85" t="n">
         <v>0</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0</v>
       </c>
@@ -15120,9 +15078,6 @@
       <c r="P88" t="n">
         <v>0</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0</v>
       </c>
@@ -15532,9 +15487,6 @@
       <c r="P90" t="n">
         <v>0</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0</v>
       </c>
@@ -15944,9 +15896,6 @@
       <c r="P92" t="n">
         <v>0</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0</v>
       </c>
@@ -16356,9 +16305,6 @@
       <c r="P94" t="n">
         <v>0</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0</v>
       </c>
@@ -16916,9 +16862,6 @@
       <c r="P97" t="n">
         <v>0</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>0</v>
       </c>
@@ -17328,9 +17271,6 @@
       <c r="P99" t="n">
         <v>0</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0</v>
       </c>
@@ -17740,9 +17680,6 @@
       <c r="P101" t="n">
         <v>0</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>0</v>
       </c>
@@ -18152,9 +18089,6 @@
       <c r="P103" t="n">
         <v>0</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0</v>
       </c>
@@ -18712,9 +18646,6 @@
       <c r="P106" t="n">
         <v>0</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0</v>
       </c>
@@ -19124,9 +19055,6 @@
       <c r="P108" t="n">
         <v>0</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0</v>
       </c>
@@ -19536,9 +19464,6 @@
       <c r="P110" t="n">
         <v>0</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0</v>
       </c>
@@ -19948,9 +19873,6 @@
       <c r="P112" t="n">
         <v>0</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0</v>
       </c>
@@ -20358,9 +20280,6 @@
         <v>0</v>
       </c>
       <c r="P114" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q114" t="n">
         <v>0</v>
       </c>
       <c r="R114" t="n">
